--- a/Hoadon/HD2026/HDRa/1/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDRa/1/3502550210_HDDienTuMayTinhTien.xlsx
@@ -5772,58 +5772,882 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E89" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F89" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G89" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H89" s="7"/>
+      <c r="I89" s="6"/>
+      <c r="J89" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K89" s="6"/>
+      <c r="L89" s="13" t="n">
+        <v>5224214.0</v>
+      </c>
+      <c r="M89" s="13" t="n">
+        <v>445311.0</v>
+      </c>
+      <c r="N89" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O89" s="13" t="n">
+        <v>5669525.0</v>
+      </c>
+      <c r="P89" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q89" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>84.0</v>
+      </c>
+      <c r="B90" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C90" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E90" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F90" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G90" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H90" s="7"/>
+      <c r="I90" s="6"/>
+      <c r="J90" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K90" s="6"/>
+      <c r="L90" s="13" t="n">
+        <v>9419615.0</v>
+      </c>
+      <c r="M90" s="13" t="n">
+        <v>825387.0</v>
+      </c>
+      <c r="N90" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O90" s="13" t="n">
+        <v>1.0245002E7</v>
+      </c>
+      <c r="P90" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q90" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>85.0</v>
+      </c>
+      <c r="B91" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E91" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F91" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G91" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H91" s="7"/>
+      <c r="I91" s="6"/>
+      <c r="J91" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K91" s="6"/>
+      <c r="L91" s="13" t="n">
+        <v>8100700.0</v>
+      </c>
+      <c r="M91" s="13" t="n">
+        <v>678966.0</v>
+      </c>
+      <c r="N91" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O91" s="13" t="n">
+        <v>8779666.0</v>
+      </c>
+      <c r="P91" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q91" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>86.0</v>
+      </c>
+      <c r="B92" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C92" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E92" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F92" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G92" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H92" s="7"/>
+      <c r="I92" s="6"/>
+      <c r="J92" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K92" s="6"/>
+      <c r="L92" s="13" t="n">
+        <v>8901234.0</v>
+      </c>
+      <c r="M92" s="13" t="n">
+        <v>862195.0</v>
+      </c>
+      <c r="N92" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O92" s="13" t="n">
+        <v>9763429.0</v>
+      </c>
+      <c r="P92" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q92" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>87.0</v>
+      </c>
+      <c r="B93" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C93" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E93" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F93" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G93" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H93" s="7"/>
+      <c r="I93" s="6" t="inlineStr">
+        <is>
+          <t>NGUYỄN THỊ HẢI BÌNH</t>
+        </is>
+      </c>
+      <c r="J93" s="6" t="inlineStr">
+        <is>
+          <t>199 Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K93" s="6" t="inlineStr">
+        <is>
+          <t>033189005308</t>
+        </is>
+      </c>
+      <c r="L93" s="13" t="n">
+        <v>3389233.0</v>
+      </c>
+      <c r="M93" s="13" t="n">
+        <v>297220.0</v>
+      </c>
+      <c r="N93" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O93" s="13" t="n">
+        <v>3686453.0</v>
+      </c>
+      <c r="P93" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q93" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>88.0</v>
+      </c>
+      <c r="B94" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E94" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F94" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G94" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H94" s="7"/>
+      <c r="I94" s="6" t="inlineStr">
+        <is>
+          <t>Trần Thanh Hưng</t>
+        </is>
+      </c>
+      <c r="J94" s="6" t="inlineStr">
+        <is>
+          <t>507 B đường 2/9, Phường Rạch Dừa Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K94" s="6" t="inlineStr">
+        <is>
+          <t>052090000956</t>
+        </is>
+      </c>
+      <c r="L94" s="13" t="n">
+        <v>2702706.0</v>
+      </c>
+      <c r="M94" s="13" t="n">
+        <v>244289.0</v>
+      </c>
+      <c r="N94" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O94" s="13" t="n">
+        <v>2946995.0</v>
+      </c>
+      <c r="P94" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q94" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>89.0</v>
+      </c>
+      <c r="B95" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="E89" s="7" t="inlineStr">
+      <c r="E95" s="7" t="inlineStr">
         <is>
           <t>02/01/2026</t>
         </is>
       </c>
-      <c r="F89" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="G89" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
-        </is>
-      </c>
-      <c r="H89" s="7"/>
-      <c r="I89" s="6" t="inlineStr">
+      <c r="F95" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G95" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H95" s="7"/>
+      <c r="I95" s="6" t="inlineStr">
         <is>
           <t>Phạm Thị Trúc Mai</t>
         </is>
       </c>
-      <c r="J89" s="6" t="inlineStr">
+      <c r="J95" s="6" t="inlineStr">
         <is>
           <t>34/11 A Lương Văn Can Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
-      <c r="K89" s="6" t="inlineStr">
+      <c r="K95" s="6" t="inlineStr">
         <is>
           <t>086185004284</t>
         </is>
       </c>
-      <c r="L89" s="13" t="n">
+      <c r="L95" s="13" t="n">
         <v>7325388.0</v>
       </c>
-      <c r="M89" s="13" t="n">
+      <c r="M95" s="13" t="n">
         <v>689632.0</v>
       </c>
-      <c r="N89" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O89" s="13" t="n">
+      <c r="N95" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O95" s="13" t="n">
         <v>8015020.0</v>
       </c>
-      <c r="P89" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q89" s="6" t="inlineStr">
+      <c r="P95" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q95" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>90.0</v>
+      </c>
+      <c r="B96" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E96" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F96" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G96" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H96" s="7"/>
+      <c r="I96" s="6"/>
+      <c r="J96" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K96" s="6"/>
+      <c r="L96" s="13" t="n">
+        <v>8943696.0</v>
+      </c>
+      <c r="M96" s="13" t="n">
+        <v>868221.0</v>
+      </c>
+      <c r="N96" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O96" s="13" t="n">
+        <v>9811917.0</v>
+      </c>
+      <c r="P96" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q96" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>91.0</v>
+      </c>
+      <c r="B97" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E97" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F97" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G97" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H97" s="7"/>
+      <c r="I97" s="6"/>
+      <c r="J97" s="6" t="inlineStr">
+        <is>
+          <t>135/2 C LÊ QUANG ĐỊNH PHƯỜNG RẠCH DỪA THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="K97" s="6" t="inlineStr">
+        <is>
+          <t>077194008987</t>
+        </is>
+      </c>
+      <c r="L97" s="13" t="n">
+        <v>3498983.0</v>
+      </c>
+      <c r="M97" s="13" t="n">
+        <v>289082.0</v>
+      </c>
+      <c r="N97" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O97" s="13" t="n">
+        <v>3788065.0</v>
+      </c>
+      <c r="P97" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q97" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>92.0</v>
+      </c>
+      <c r="B98" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E98" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F98" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G98" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H98" s="7"/>
+      <c r="I98" s="6" t="inlineStr">
+        <is>
+          <t>Cô Vân . 790 trần phú</t>
+        </is>
+      </c>
+      <c r="J98" s="6" t="inlineStr">
+        <is>
+          <t>790 trần phú, Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K98" s="6" t="inlineStr">
+        <is>
+          <t>075159002802</t>
+        </is>
+      </c>
+      <c r="L98" s="13" t="n">
+        <v>4797624.0</v>
+      </c>
+      <c r="M98" s="13" t="n">
+        <v>448689.0</v>
+      </c>
+      <c r="N98" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O98" s="13" t="n">
+        <v>5246313.0</v>
+      </c>
+      <c r="P98" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q98" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>93.0</v>
+      </c>
+      <c r="B99" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E99" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F99" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G99" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H99" s="7"/>
+      <c r="I99" s="6"/>
+      <c r="J99" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K99" s="6"/>
+      <c r="L99" s="13" t="n">
+        <v>1.0657357E7</v>
+      </c>
+      <c r="M99" s="13" t="n">
+        <v>1025737.0</v>
+      </c>
+      <c r="N99" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O99" s="13" t="n">
+        <v>1.1683094E7</v>
+      </c>
+      <c r="P99" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q99" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>94.0</v>
+      </c>
+      <c r="B100" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D100" s="7" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E100" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F100" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G100" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H100" s="7" t="inlineStr">
+        <is>
+          <t>3502556808</t>
+        </is>
+      </c>
+      <c r="I100" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI THỦY HẢI SẢN KIM NGÂN</t>
+        </is>
+      </c>
+      <c r="J100" s="6" t="inlineStr">
+        <is>
+          <t>Số 65A Yên Bái, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K100" s="6"/>
+      <c r="L100" s="13" t="n">
+        <v>8499975.0</v>
+      </c>
+      <c r="M100" s="13" t="n">
+        <v>849998.0</v>
+      </c>
+      <c r="N100" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O100" s="13" t="n">
+        <v>9349973.0</v>
+      </c>
+      <c r="P100" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q100" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>95.0</v>
+      </c>
+      <c r="B101" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E101" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F101" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G101" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H101" s="7" t="inlineStr">
+        <is>
+          <t>077088009229</t>
+        </is>
+      </c>
+      <c r="I101" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH TÂM NGUYỄN (DƯƠNG THẾ HUY)</t>
+        </is>
+      </c>
+      <c r="J101" s="6" t="inlineStr">
+        <is>
+          <t>04 đường Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K101" s="6"/>
+      <c r="L101" s="13" t="n">
+        <v>4.2926212E7</v>
+      </c>
+      <c r="M101" s="13" t="n">
+        <v>4049441.0</v>
+      </c>
+      <c r="N101" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O101" s="13" t="n">
+        <v>4.6975653E7</v>
+      </c>
+      <c r="P101" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q101" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HD2026/HDRa/1/3502550210_HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HD2026/HDRa/1/3502550210_HDDienTuMayTinhTien.xlsx
@@ -448,12 +448,12 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>100</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
@@ -475,16 +475,16 @@
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>8983468.0</v>
+        <v>5722130.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>848497.0</v>
+        <v>457770.0</v>
       </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>9831965.0</v>
+        <v>6179900.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -513,12 +513,12 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -532,32 +532,24 @@
         </is>
       </c>
       <c r="H10" s="7"/>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Đào Việt Anh</t>
-        </is>
-      </c>
+      <c r="I10" s="6"/>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>89/1 Mạc Đỉnh Chi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K10" s="6" t="inlineStr">
-        <is>
-          <t>031083020502</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K10" s="6"/>
       <c r="L10" s="13" t="n">
-        <v>4688016.0</v>
+        <v>6870320.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>422222.0</v>
+        <v>549625.0</v>
       </c>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>5110238.0</v>
+        <v>7419945.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -586,12 +578,12 @@
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>102</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -605,24 +597,24 @@
         </is>
       </c>
       <c r="H11" s="7"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6" t="inlineStr">
-        <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J11" s="6"/>
       <c r="K11" s="6"/>
       <c r="L11" s="13" t="n">
-        <v>9175682.0</v>
+        <v>5284088.0</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>886289.0</v>
+        <v>520353.0</v>
       </c>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>1.0061971E7</v>
+        <v>5804441.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -651,12 +643,12 @@
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>103</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -672,30 +664,22 @@
       <c r="H12" s="7"/>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>Nguyễn Thị Ngọc Loan</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
-        <is>
-          <t>61/2/1 Nguyễn An Ninh, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K12" s="6" t="inlineStr">
-        <is>
-          <t>077184005373</t>
-        </is>
-      </c>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
       <c r="L12" s="13" t="n">
-        <v>6750300.0</v>
+        <v>5284088.0</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>641790.0</v>
+        <v>520353.0</v>
       </c>
       <c r="N12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>7392090.0</v>
+        <v>5804441.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -724,12 +708,12 @@
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>104</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
@@ -743,24 +727,24 @@
         </is>
       </c>
       <c r="H13" s="7"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6" t="inlineStr">
-        <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J13" s="6"/>
       <c r="K13" s="6"/>
       <c r="L13" s="13" t="n">
-        <v>4664450.0</v>
+        <v>5284088.0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>446113.0</v>
+        <v>520353.0</v>
       </c>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>5110563.0</v>
+        <v>5804441.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -789,12 +773,12 @@
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>105</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
@@ -808,24 +792,24 @@
         </is>
       </c>
       <c r="H14" s="7"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6" t="inlineStr">
-        <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J14" s="6"/>
       <c r="K14" s="6"/>
       <c r="L14" s="13" t="n">
-        <v>5416085.0</v>
+        <v>5284088.0</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>500560.0</v>
+        <v>520353.0</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>5916645.0</v>
+        <v>5804441.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -854,12 +838,12 @@
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>106</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
@@ -873,28 +857,32 @@
         </is>
       </c>
       <c r="H15" s="7"/>
-      <c r="I15" s="6"/>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>Thảo mạng</t>
+        </is>
+      </c>
       <c r="J15" s="6" t="inlineStr">
         <is>
-          <t>122/29 Lý Tự Trọng Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+          <t>trần Phú</t>
         </is>
       </c>
       <c r="K15" s="6" t="inlineStr">
         <is>
-          <t>093083010956</t>
+          <t>051184000686</t>
         </is>
       </c>
       <c r="L15" s="13" t="n">
-        <v>5539764.0</v>
+        <v>1871615.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>543161.0</v>
+        <v>168438.0</v>
       </c>
       <c r="N15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>6082925.0</v>
+        <v>2040053.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -923,12 +911,12 @@
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>107</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
@@ -942,24 +930,32 @@
         </is>
       </c>
       <c r="H16" s="7"/>
-      <c r="I16" s="6"/>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>Thảo mạng</t>
+        </is>
+      </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K16" s="6"/>
+          <t>trần Phú</t>
+        </is>
+      </c>
+      <c r="K16" s="6" t="inlineStr">
+        <is>
+          <t>051184000686</t>
+        </is>
+      </c>
       <c r="L16" s="13" t="n">
-        <v>2.67272E7</v>
+        <v>1871615.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>2672720.0</v>
+        <v>168438.0</v>
       </c>
       <c r="N16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>2.939992E7</v>
+        <v>2040053.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -988,12 +984,12 @@
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
@@ -1007,24 +1003,32 @@
         </is>
       </c>
       <c r="H17" s="7"/>
-      <c r="I17" s="6"/>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>Thảo mạng</t>
+        </is>
+      </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K17" s="6"/>
+          <t>trần Phú</t>
+        </is>
+      </c>
+      <c r="K17" s="6" t="inlineStr">
+        <is>
+          <t>051184000686</t>
+        </is>
+      </c>
       <c r="L17" s="13" t="n">
-        <v>3183232.0</v>
+        <v>1871615.0</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>258768.0</v>
+        <v>168438.0</v>
       </c>
       <c r="N17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>3442000.0</v>
+        <v>2040053.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -1053,12 +1057,12 @@
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>109</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
@@ -1075,25 +1079,21 @@
       <c r="I18" s="6"/>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>57/8 A Nguyễn Hữu  Cảnh, Phường Rạch Dừa Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K18" s="6" t="inlineStr">
-        <is>
-          <t>093185007857</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K18" s="6"/>
       <c r="L18" s="13" t="n">
-        <v>5224742.0</v>
+        <v>1.0942482E7</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>490251.0</v>
+        <v>1011265.0</v>
       </c>
       <c r="N18" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>5714993.0</v>
+        <v>1.1953747E7</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>11</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>03/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
@@ -1149,16 +1149,16 @@
       </c>
       <c r="K19" s="6"/>
       <c r="L19" s="13" t="n">
-        <v>7609536.0</v>
+        <v>8983468.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>743266.0</v>
+        <v>848497.0</v>
       </c>
       <c r="N19" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>8352802.0</v>
+        <v>9831965.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>110</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -1214,16 +1214,16 @@
       </c>
       <c r="K20" s="6"/>
       <c r="L20" s="13" t="n">
-        <v>4.00908E7</v>
+        <v>5411995.0</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>4009080.0</v>
+        <v>432959.0</v>
       </c>
       <c r="N20" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>4.409988E7</v>
+        <v>5844954.0</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>111</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
@@ -1279,16 +1279,16 @@
       </c>
       <c r="K21" s="6"/>
       <c r="L21" s="13" t="n">
-        <v>1.18182E7</v>
+        <v>7640299.0</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>1181820.0</v>
+        <v>727086.0</v>
       </c>
       <c r="N21" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>1.300002E7</v>
+        <v>8367385.0</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -1317,12 +1317,12 @@
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>112</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
@@ -1335,33 +1335,25 @@
           <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
-      <c r="H22" s="7" t="inlineStr">
-        <is>
-          <t>010175001031</t>
-        </is>
-      </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>HỘ KINH DOANH VŨ THỊ HỒNG LOAN (NGỌC BẢO)</t>
-        </is>
-      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="6"/>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>13 đường Bùi Thiện Ngộ, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>khách lẻ không lấy hóa đơn</t>
         </is>
       </c>
       <c r="K22" s="6"/>
       <c r="L22" s="13" t="n">
-        <v>9818150.0</v>
+        <v>7066332.0</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>981815.0</v>
+        <v>682782.0</v>
       </c>
       <c r="N22" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>1.0799965E7</v>
+        <v>7749114.0</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -1390,12 +1382,12 @@
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>113</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>04/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
@@ -1408,33 +1400,25 @@
           <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
-      <c r="H23" s="7" t="inlineStr">
-        <is>
-          <t>077088009229</t>
-        </is>
-      </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>HỘ KINH DOANH TÂM NGUYỄN (DƯƠNG THẾ HUY)</t>
-        </is>
-      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="6"/>
       <c r="J23" s="6" t="inlineStr">
         <is>
-          <t>04 đường Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+          <t>khách lẻ không lấy hóa đơn</t>
         </is>
       </c>
       <c r="K23" s="6"/>
       <c r="L23" s="13" t="n">
-        <v>4.896766E7</v>
+        <v>9446527.0</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>4488479.0</v>
+        <v>941319.0</v>
       </c>
       <c r="N23" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>5.3456139E7</v>
+        <v>1.0387846E7</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -1463,12 +1447,12 @@
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>114</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
@@ -1490,16 +1474,16 @@
       </c>
       <c r="K24" s="6"/>
       <c r="L24" s="13" t="n">
-        <v>7896465.0</v>
+        <v>6991110.0</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>789647.0</v>
+        <v>689388.0</v>
       </c>
       <c r="N24" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>8686112.0</v>
+        <v>7680498.0</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -1528,12 +1512,12 @@
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>115</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -1550,25 +1534,21 @@
       <c r="I25" s="6"/>
       <c r="J25" s="6" t="inlineStr">
         <is>
-          <t>107/12*/1 Bình giã</t>
-        </is>
-      </c>
-      <c r="K25" s="6" t="inlineStr">
-        <is>
-          <t>093185007857</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K25" s="6"/>
       <c r="L25" s="13" t="n">
-        <v>6224146.0</v>
+        <v>6851723.0</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>620971.0</v>
+        <v>682858.0</v>
       </c>
       <c r="N25" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>6845117.0</v>
+        <v>7534581.0</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -1597,12 +1577,12 @@
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>116</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -1616,32 +1596,24 @@
         </is>
       </c>
       <c r="H26" s="7"/>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Ngọc Loan</t>
-        </is>
-      </c>
+      <c r="I26" s="6"/>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>61/2/1 Nguyễn An Ninh, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K26" s="6" t="inlineStr">
-        <is>
-          <t>077184005373</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K26" s="6"/>
       <c r="L26" s="13" t="n">
-        <v>6467909.0</v>
+        <v>2037030.0</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>633069.0</v>
+        <v>162962.0</v>
       </c>
       <c r="N26" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>7100978.0</v>
+        <v>2199992.0</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
@@ -1670,12 +1642,12 @@
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>117</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -1697,16 +1669,16 @@
       </c>
       <c r="K27" s="6"/>
       <c r="L27" s="13" t="n">
-        <v>7908337.0</v>
+        <v>5567889.0</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>766000.0</v>
+        <v>529605.0</v>
       </c>
       <c r="N27" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>8674337.0</v>
+        <v>6097494.0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -1735,12 +1707,12 @@
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>118</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -1762,16 +1734,16 @@
       </c>
       <c r="K28" s="6"/>
       <c r="L28" s="13" t="n">
-        <v>8204313.0</v>
+        <v>7250146.0</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>746282.0</v>
+        <v>723404.0</v>
       </c>
       <c r="N28" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>8950595.0</v>
+        <v>7973550.0</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -1800,12 +1772,12 @@
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>119</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -1827,16 +1799,16 @@
       </c>
       <c r="K29" s="6"/>
       <c r="L29" s="13" t="n">
-        <v>5429965.0</v>
+        <v>7828170.0</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>480034.0</v>
+        <v>782817.0</v>
       </c>
       <c r="N29" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>5909999.0</v>
+        <v>8610987.0</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1865,12 +1837,12 @@
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>12</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -1884,24 +1856,32 @@
         </is>
       </c>
       <c r="H30" s="7"/>
-      <c r="I30" s="6"/>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>Đào Việt Anh</t>
+        </is>
+      </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K30" s="6"/>
+          <t>89/1 Mạc Đỉnh Chi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K30" s="6" t="inlineStr">
+        <is>
+          <t>031083020502</t>
+        </is>
+      </c>
       <c r="L30" s="13" t="n">
-        <v>1.3707389E7</v>
+        <v>4688016.0</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>1330348.0</v>
+        <v>422222.0</v>
       </c>
       <c r="N30" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>1.5037737E7</v>
+        <v>5110238.0</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -1930,12 +1910,12 @@
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>120</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -1949,32 +1929,24 @@
         </is>
       </c>
       <c r="H31" s="7"/>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>Phạm Thị Trúc Mai</t>
-        </is>
-      </c>
+      <c r="I31" s="6"/>
       <c r="J31" s="6" t="inlineStr">
         <is>
-          <t>34/11 A Lương Văn Can Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K31" s="6" t="inlineStr">
-        <is>
-          <t>086185004284</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K31" s="6"/>
       <c r="L31" s="13" t="n">
-        <v>1.003315E7</v>
+        <v>7097685.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>996834.0</v>
+        <v>662360.0</v>
       </c>
       <c r="N31" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>1.1029984E7</v>
+        <v>7760045.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -2003,12 +1975,12 @@
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>121</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>12/01/2026</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2021,29 +1993,33 @@
           <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
-      <c r="H32" s="7"/>
-      <c r="I32" s="6"/>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>010175001031</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH VŨ THỊ HỒNG LOAN (NGỌC BẢO)</t>
+        </is>
+      </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>118 Nguyễn Văn Trỗi Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="inlineStr">
-        <is>
-          <t>077166000908</t>
-        </is>
-      </c>
+          <t>13 đường Bùi Thiện Ngộ, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K32" s="6"/>
       <c r="L32" s="13" t="n">
-        <v>1.4553736E7</v>
+        <v>2.65456E7</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>1433281.0</v>
+        <v>2654560.0</v>
       </c>
       <c r="N32" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>1.5987017E7</v>
+        <v>2.920016E7</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -2072,12 +2048,12 @@
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>122</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2091,24 +2067,32 @@
         </is>
       </c>
       <c r="H33" s="7"/>
-      <c r="I33" s="6"/>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>Thảo mạng</t>
+        </is>
+      </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K33" s="6"/>
+          <t>trần Phú</t>
+        </is>
+      </c>
+      <c r="K33" s="6" t="inlineStr">
+        <is>
+          <t>051184000686</t>
+        </is>
+      </c>
       <c r="L33" s="13" t="n">
-        <v>1.5451766E7</v>
+        <v>1633333.0</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>1486142.0</v>
+        <v>130667.0</v>
       </c>
       <c r="N33" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>1.6937908E7</v>
+        <v>1764000.0</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -2137,12 +2121,12 @@
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2159,25 +2143,21 @@
       <c r="I34" s="6"/>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>135/2 C LÊ QUANG ĐỊNH PHƯỜNG RẠCH DỪA THÀNH PHỐ HỒ CHÍ MINH</t>
-        </is>
-      </c>
-      <c r="K34" s="6" t="inlineStr">
-        <is>
-          <t>077194008987</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K34" s="6"/>
       <c r="L34" s="13" t="n">
-        <v>1.0729805E7</v>
+        <v>9071755.0</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>978203.0</v>
+        <v>907176.0</v>
       </c>
       <c r="N34" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>1.1708008E7</v>
+        <v>9978931.0</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -2206,12 +2186,12 @@
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>124</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -2233,16 +2213,16 @@
       </c>
       <c r="K35" s="6"/>
       <c r="L35" s="13" t="n">
-        <v>1.2458547E7</v>
+        <v>1.0796461E7</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>1216986.0</v>
+        <v>1053535.0</v>
       </c>
       <c r="N35" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O35" s="13" t="n">
-        <v>1.3675533E7</v>
+        <v>1.1849996E7</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -2271,12 +2251,12 @@
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>125</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -2298,16 +2278,16 @@
       </c>
       <c r="K36" s="6"/>
       <c r="L36" s="13" t="n">
-        <v>1.166661E7</v>
+        <v>8127737.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>1101651.0</v>
+        <v>720626.0</v>
       </c>
       <c r="N36" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>1.2768261E7</v>
+        <v>8848363.0</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
@@ -2336,12 +2316,12 @@
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>126</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -2358,25 +2338,21 @@
       <c r="I37" s="6"/>
       <c r="J37" s="6" t="inlineStr">
         <is>
-          <t>76 ĐƯỜNG 30/4 PHƯỜNG RẠCH DỪA THÀNH PHỐ HỒ CHÍ MINH</t>
-        </is>
-      </c>
-      <c r="K37" s="6" t="inlineStr">
-        <is>
-          <t>094195002314</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K37" s="6"/>
       <c r="L37" s="13" t="n">
-        <v>6950886.0</v>
+        <v>8305575.0</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>643014.0</v>
+        <v>680001.0</v>
       </c>
       <c r="N37" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>7593900.0</v>
+        <v>8985576.0</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
@@ -2405,12 +2381,12 @@
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>127</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>14/01/2026</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -2432,16 +2408,16 @@
       </c>
       <c r="K38" s="6"/>
       <c r="L38" s="13" t="n">
-        <v>5382429.0</v>
+        <v>8397123.0</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>511426.0</v>
+        <v>671770.0</v>
       </c>
       <c r="N38" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>5893855.0</v>
+        <v>9068893.0</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
@@ -2470,12 +2446,12 @@
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>13</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>05/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -2497,16 +2473,16 @@
       </c>
       <c r="K39" s="6"/>
       <c r="L39" s="13" t="n">
-        <v>4944615.0</v>
+        <v>9175682.0</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>436294.0</v>
+        <v>886289.0</v>
       </c>
       <c r="N39" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>5380909.0</v>
+        <v>1.0061971E7</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -2535,12 +2511,12 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>14</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -2554,24 +2530,32 @@
         </is>
       </c>
       <c r="H40" s="7"/>
-      <c r="I40" s="6"/>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Ngọc Loan</t>
+        </is>
+      </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K40" s="6"/>
+          <t>61/2/1 Nguyễn An Ninh, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K40" s="6" t="inlineStr">
+        <is>
+          <t>077184005373</t>
+        </is>
+      </c>
       <c r="L40" s="13" t="n">
-        <v>6936482.0</v>
+        <v>6750300.0</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>612501.0</v>
+        <v>641790.0</v>
       </c>
       <c r="N40" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O40" s="13" t="n">
-        <v>7548983.0</v>
+        <v>7392090.0</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -2600,12 +2584,12 @@
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -2618,33 +2602,25 @@
           <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
-      <c r="H41" s="7" t="inlineStr">
-        <is>
-          <t>010175001031</t>
-        </is>
-      </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>HỘ KINH DOANH VŨ THỊ HỒNG LOAN (NGỌC BẢO)</t>
-        </is>
-      </c>
+      <c r="H41" s="7"/>
+      <c r="I41" s="6"/>
       <c r="J41" s="6" t="inlineStr">
         <is>
-          <t>13 đường Bùi Thiện Ngộ, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+          <t>khách lẻ không lấy hóa đơn</t>
         </is>
       </c>
       <c r="K41" s="6"/>
       <c r="L41" s="13" t="n">
-        <v>6636350.0</v>
+        <v>4664450.0</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>663635.0</v>
+        <v>446113.0</v>
       </c>
       <c r="N41" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O41" s="13" t="n">
-        <v>7299985.0</v>
+        <v>5110563.0</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -2673,12 +2649,12 @@
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>41</t>
+          <t>16</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -2700,16 +2676,16 @@
       </c>
       <c r="K42" s="6"/>
       <c r="L42" s="13" t="n">
-        <v>5568181.0</v>
+        <v>5416085.0</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>545429.0</v>
+        <v>500560.0</v>
       </c>
       <c r="N42" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O42" s="13" t="n">
-        <v>6113610.0</v>
+        <v>5916645.0</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -2738,12 +2714,12 @@
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>17</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -2758,19 +2734,27 @@
       </c>
       <c r="H43" s="7"/>
       <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
-      <c r="K43" s="6"/>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>122/29 Lý Tự Trọng Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K43" s="6" t="inlineStr">
+        <is>
+          <t>093083010956</t>
+        </is>
+      </c>
       <c r="L43" s="13" t="n">
-        <v>2.67272E7</v>
+        <v>5539764.0</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>2672720.0</v>
+        <v>543161.0</v>
       </c>
       <c r="N43" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O43" s="13" t="n">
-        <v>2.939992E7</v>
+        <v>6082925.0</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -2799,12 +2783,12 @@
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>18</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -2818,32 +2802,24 @@
         </is>
       </c>
       <c r="H44" s="7"/>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>268/15 Trần Phú</t>
-        </is>
-      </c>
+      <c r="I44" s="6"/>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>268/15 Trần Phú , Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K44" s="6" t="inlineStr">
-        <is>
-          <t>087063018418</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K44" s="6"/>
       <c r="L44" s="13" t="n">
-        <v>3.4669524E7</v>
+        <v>2.67272E7</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>3385479.0</v>
+        <v>2672720.0</v>
       </c>
       <c r="N44" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O44" s="13" t="n">
-        <v>3.8055003E7</v>
+        <v>2.939992E7</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
@@ -2872,12 +2848,12 @@
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>19</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -2891,32 +2867,24 @@
         </is>
       </c>
       <c r="H45" s="7"/>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>Trần Thanh Hưng</t>
-        </is>
-      </c>
+      <c r="I45" s="6"/>
       <c r="J45" s="6" t="inlineStr">
         <is>
-          <t>507 B đường 2/9, Phường Rạch Dừa Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K45" s="6" t="inlineStr">
-        <is>
-          <t>052090000956</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K45" s="6"/>
       <c r="L45" s="13" t="n">
-        <v>8072183.0</v>
+        <v>3183232.0</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>726721.0</v>
+        <v>258768.0</v>
       </c>
       <c r="N45" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O45" s="13" t="n">
-        <v>8798904.0</v>
+        <v>3442000.0</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
@@ -2945,12 +2913,12 @@
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -2967,21 +2935,25 @@
       <c r="I46" s="6"/>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K46" s="6"/>
+          <t>57/8 A Nguyễn Hữu  Cảnh, Phường Rạch Dừa Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K46" s="6" t="inlineStr">
+        <is>
+          <t>093185007857</t>
+        </is>
+      </c>
       <c r="L46" s="13" t="n">
-        <v>1.153345E7</v>
+        <v>5224742.0</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>1146234.0</v>
+        <v>490251.0</v>
       </c>
       <c r="N46" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O46" s="13" t="n">
-        <v>1.2679684E7</v>
+        <v>5714993.0</v>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
@@ -3010,12 +2982,12 @@
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>20</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>03/01/2026</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3029,32 +3001,24 @@
         </is>
       </c>
       <c r="H47" s="7"/>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>NGUYỄN THỊ HẢI BÌNH</t>
-        </is>
-      </c>
+      <c r="I47" s="6"/>
       <c r="J47" s="6" t="inlineStr">
         <is>
-          <t>199 Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K47" s="6" t="inlineStr">
-        <is>
-          <t>033189005308</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K47" s="6"/>
       <c r="L47" s="13" t="n">
-        <v>8792609.0</v>
+        <v>7609536.0</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>839465.0</v>
+        <v>743266.0</v>
       </c>
       <c r="N47" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O47" s="13" t="n">
-        <v>9632074.0</v>
+        <v>8352802.0</v>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
@@ -3083,12 +3047,12 @@
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>21</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>06/01/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -3110,16 +3074,16 @@
       </c>
       <c r="K48" s="6"/>
       <c r="L48" s="13" t="n">
-        <v>9664240.0</v>
+        <v>4.00908E7</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>961591.0</v>
+        <v>4009080.0</v>
       </c>
       <c r="N48" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O48" s="13" t="n">
-        <v>1.0625831E7</v>
+        <v>4.409988E7</v>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
@@ -3148,12 +3112,12 @@
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>48</t>
+          <t>22</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -3175,16 +3139,16 @@
       </c>
       <c r="K49" s="6"/>
       <c r="L49" s="13" t="n">
-        <v>5899396.0</v>
+        <v>1.18182E7</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>554088.0</v>
+        <v>1181820.0</v>
       </c>
       <c r="N49" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O49" s="13" t="n">
-        <v>6453484.0</v>
+        <v>1.300002E7</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
@@ -3213,12 +3177,12 @@
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>23</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -3231,33 +3195,33 @@
           <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
-      <c r="H50" s="7"/>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>010175001031</t>
+        </is>
+      </c>
       <c r="I50" s="6" t="inlineStr">
         <is>
-          <t>Cô Vân . 790 trần phú</t>
+          <t>HỘ KINH DOANH VŨ THỊ HỒNG LOAN (NGỌC BẢO)</t>
         </is>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>790 trần phú, Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K50" s="6" t="inlineStr">
-        <is>
-          <t>075159002802</t>
-        </is>
-      </c>
+          <t>13 đường Bùi Thiện Ngộ, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K50" s="6"/>
       <c r="L50" s="13" t="n">
-        <v>3314238.0</v>
+        <v>9818150.0</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>312720.0</v>
+        <v>981815.0</v>
       </c>
       <c r="N50" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O50" s="13" t="n">
-        <v>3626958.0</v>
+        <v>1.0799965E7</v>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
@@ -3286,12 +3250,12 @@
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>24</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>04/01/2026</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -3304,29 +3268,33 @@
           <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
-      <c r="H51" s="7"/>
-      <c r="I51" s="6"/>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>077088009229</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH TÂM NGUYỄN (DƯƠNG THẾ HUY)</t>
+        </is>
+      </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
-          <t>1507/2 A Đường 30/4 Phường Phước Thắng Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K51" s="6" t="inlineStr">
-        <is>
-          <t>077096003835</t>
-        </is>
-      </c>
+          <t>04 đường Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K51" s="6"/>
       <c r="L51" s="13" t="n">
-        <v>8122536.0</v>
+        <v>4.896766E7</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>748462.0</v>
+        <v>4488479.0</v>
       </c>
       <c r="N51" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O51" s="13" t="n">
-        <v>8870998.0</v>
+        <v>5.3456139E7</v>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
@@ -3355,12 +3323,12 @@
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -3382,16 +3350,16 @@
       </c>
       <c r="K52" s="6"/>
       <c r="L52" s="13" t="n">
-        <v>1.0153298E7</v>
+        <v>7896465.0</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>998237.0</v>
+        <v>789647.0</v>
       </c>
       <c r="N52" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O52" s="13" t="n">
-        <v>1.1151535E7</v>
+        <v>8686112.0</v>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
@@ -3420,12 +3388,12 @@
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>26</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -3442,21 +3410,25 @@
       <c r="I53" s="6"/>
       <c r="J53" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K53" s="6"/>
+          <t>107/12*/1 Bình giã</t>
+        </is>
+      </c>
+      <c r="K53" s="6" t="inlineStr">
+        <is>
+          <t>093185007857</t>
+        </is>
+      </c>
       <c r="L53" s="13" t="n">
-        <v>5879236.0</v>
+        <v>6224146.0</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>543793.0</v>
+        <v>620971.0</v>
       </c>
       <c r="N53" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O53" s="13" t="n">
-        <v>6423029.0</v>
+        <v>6845117.0</v>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
@@ -3485,12 +3457,12 @@
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>52</t>
+          <t>27</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -3504,28 +3476,32 @@
         </is>
       </c>
       <c r="H54" s="7"/>
-      <c r="I54" s="6"/>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>Nguyễn Thị Ngọc Loan</t>
+        </is>
+      </c>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>118 Nguyễn Văn Trỗi Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+          <t>61/2/1 Nguyễn An Ninh, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr">
         <is>
-          <t>077166000908</t>
+          <t>077184005373</t>
         </is>
       </c>
       <c r="L54" s="13" t="n">
-        <v>8333944.0</v>
+        <v>6467909.0</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>772875.0</v>
+        <v>633069.0</v>
       </c>
       <c r="N54" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O54" s="13" t="n">
-        <v>9106819.0</v>
+        <v>7100978.0</v>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
@@ -3554,12 +3530,12 @@
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>28</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -3573,32 +3549,24 @@
         </is>
       </c>
       <c r="H55" s="7"/>
-      <c r="I55" s="6" t="inlineStr">
-        <is>
-          <t>Nguyễn Thị Ngọc Châu</t>
-        </is>
-      </c>
+      <c r="I55" s="6"/>
       <c r="J55" s="6" t="inlineStr">
         <is>
-          <t>61/2/1 Nguyễn An Ninh, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K55" s="6" t="inlineStr">
-        <is>
-          <t>077190007452</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K55" s="6"/>
       <c r="L55" s="13" t="n">
-        <v>7741616.0</v>
+        <v>7908337.0</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>742717.0</v>
+        <v>766000.0</v>
       </c>
       <c r="N55" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O55" s="13" t="n">
-        <v>8484333.0</v>
+        <v>8674337.0</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
@@ -3627,12 +3595,12 @@
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>54</t>
+          <t>29</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -3654,16 +3622,16 @@
       </c>
       <c r="K56" s="6"/>
       <c r="L56" s="13" t="n">
-        <v>1.0576309E7</v>
+        <v>8204313.0</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>981057.0</v>
+        <v>746282.0</v>
       </c>
       <c r="N56" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O56" s="13" t="n">
-        <v>1.1557366E7</v>
+        <v>8950595.0</v>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
@@ -3692,12 +3660,12 @@
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>3</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -3719,16 +3687,16 @@
       </c>
       <c r="K57" s="6"/>
       <c r="L57" s="13" t="n">
-        <v>8964622.0</v>
+        <v>5429965.0</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>859241.0</v>
+        <v>480034.0</v>
       </c>
       <c r="N57" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O57" s="13" t="n">
-        <v>9823863.0</v>
+        <v>5909999.0</v>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
@@ -3757,12 +3725,12 @@
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>30</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
@@ -3784,16 +3752,16 @@
       </c>
       <c r="K58" s="6"/>
       <c r="L58" s="13" t="n">
-        <v>8861692.0</v>
+        <v>1.3707389E7</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>731874.0</v>
+        <v>1330348.0</v>
       </c>
       <c r="N58" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O58" s="13" t="n">
-        <v>9593566.0</v>
+        <v>1.5037737E7</v>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
@@ -3822,12 +3790,12 @@
       </c>
       <c r="D59" s="7" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>31</t>
         </is>
       </c>
       <c r="E59" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr">
@@ -3841,24 +3809,32 @@
         </is>
       </c>
       <c r="H59" s="7"/>
-      <c r="I59" s="6"/>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Thị Trúc Mai</t>
+        </is>
+      </c>
       <c r="J59" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K59" s="6"/>
+          <t>34/11 A Lương Văn Can Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K59" s="6" t="inlineStr">
+        <is>
+          <t>086185004284</t>
+        </is>
+      </c>
       <c r="L59" s="13" t="n">
-        <v>4638895.0</v>
+        <v>1.003315E7</v>
       </c>
       <c r="M59" s="13" t="n">
-        <v>371110.0</v>
+        <v>996834.0</v>
       </c>
       <c r="N59" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O59" s="13" t="n">
-        <v>5010005.0</v>
+        <v>1.1029984E7</v>
       </c>
       <c r="P59" s="6" t="inlineStr">
         <is>
@@ -3887,12 +3863,12 @@
       </c>
       <c r="D60" s="7" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>32</t>
         </is>
       </c>
       <c r="E60" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -3909,21 +3885,25 @@
       <c r="I60" s="6"/>
       <c r="J60" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K60" s="6"/>
+          <t>118 Nguyễn Văn Trỗi Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K60" s="6" t="inlineStr">
+        <is>
+          <t>077166000908</t>
+        </is>
+      </c>
       <c r="L60" s="13" t="n">
-        <v>8367763.0</v>
+        <v>1.4553736E7</v>
       </c>
       <c r="M60" s="13" t="n">
-        <v>829758.0</v>
+        <v>1433281.0</v>
       </c>
       <c r="N60" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O60" s="13" t="n">
-        <v>9197521.0</v>
+        <v>1.5987017E7</v>
       </c>
       <c r="P60" s="6" t="inlineStr">
         <is>
@@ -3952,12 +3932,12 @@
       </c>
       <c r="D61" s="7" t="inlineStr">
         <is>
-          <t>59</t>
+          <t>33</t>
         </is>
       </c>
       <c r="E61" s="7" t="inlineStr">
         <is>
-          <t>07/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -3979,16 +3959,16 @@
       </c>
       <c r="K61" s="6"/>
       <c r="L61" s="13" t="n">
-        <v>8181800.0</v>
+        <v>1.5451766E7</v>
       </c>
       <c r="M61" s="13" t="n">
-        <v>818180.0</v>
+        <v>1486142.0</v>
       </c>
       <c r="N61" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O61" s="13" t="n">
-        <v>8999980.0</v>
+        <v>1.6937908E7</v>
       </c>
       <c r="P61" s="6" t="inlineStr">
         <is>
@@ -4017,12 +3997,12 @@
       </c>
       <c r="D62" s="7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>34</t>
         </is>
       </c>
       <c r="E62" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -4039,21 +4019,25 @@
       <c r="I62" s="6"/>
       <c r="J62" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K62" s="6"/>
+          <t>135/2 C LÊ QUANG ĐỊNH PHƯỜNG RẠCH DỪA THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="K62" s="6" t="inlineStr">
+        <is>
+          <t>077194008987</t>
+        </is>
+      </c>
       <c r="L62" s="13" t="n">
-        <v>7901852.0</v>
+        <v>1.0729805E7</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>687168.0</v>
+        <v>978203.0</v>
       </c>
       <c r="N62" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>8589020.0</v>
+        <v>1.1708008E7</v>
       </c>
       <c r="P62" s="6" t="inlineStr">
         <is>
@@ -4082,12 +4066,12 @@
       </c>
       <c r="D63" s="7" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>35</t>
         </is>
       </c>
       <c r="E63" s="7" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -4109,16 +4093,16 @@
       </c>
       <c r="K63" s="6"/>
       <c r="L63" s="13" t="n">
-        <v>7954452.0</v>
+        <v>1.2458547E7</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>791371.0</v>
+        <v>1216986.0</v>
       </c>
       <c r="N63" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>8745823.0</v>
+        <v>1.3675533E7</v>
       </c>
       <c r="P63" s="6" t="inlineStr">
         <is>
@@ -4147,12 +4131,12 @@
       </c>
       <c r="D64" s="7" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>36</t>
         </is>
       </c>
       <c r="E64" s="7" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr">
@@ -4174,16 +4158,16 @@
       </c>
       <c r="K64" s="6"/>
       <c r="L64" s="13" t="n">
-        <v>8974728.0</v>
+        <v>1.166661E7</v>
       </c>
       <c r="M64" s="13" t="n">
-        <v>788888.0</v>
+        <v>1101651.0</v>
       </c>
       <c r="N64" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O64" s="13" t="n">
-        <v>9763616.0</v>
+        <v>1.2768261E7</v>
       </c>
       <c r="P64" s="6" t="inlineStr">
         <is>
@@ -4212,12 +4196,12 @@
       </c>
       <c r="D65" s="7" t="inlineStr">
         <is>
-          <t>62</t>
+          <t>37</t>
         </is>
       </c>
       <c r="E65" s="7" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr">
@@ -4234,21 +4218,25 @@
       <c r="I65" s="6"/>
       <c r="J65" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K65" s="6"/>
+          <t>76 ĐƯỜNG 30/4 PHƯỜNG RẠCH DỪA THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="K65" s="6" t="inlineStr">
+        <is>
+          <t>094195002314</t>
+        </is>
+      </c>
       <c r="L65" s="13" t="n">
-        <v>7212866.0</v>
+        <v>6950886.0</v>
       </c>
       <c r="M65" s="13" t="n">
-        <v>689529.0</v>
+        <v>643014.0</v>
       </c>
       <c r="N65" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O65" s="13" t="n">
-        <v>7902395.0</v>
+        <v>7593900.0</v>
       </c>
       <c r="P65" s="6" t="inlineStr">
         <is>
@@ -4277,12 +4265,12 @@
       </c>
       <c r="D66" s="7" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>38</t>
         </is>
       </c>
       <c r="E66" s="7" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr">
@@ -4304,16 +4292,16 @@
       </c>
       <c r="K66" s="6"/>
       <c r="L66" s="13" t="n">
-        <v>1.0307579E7</v>
+        <v>5382429.0</v>
       </c>
       <c r="M66" s="13" t="n">
-        <v>1024276.0</v>
+        <v>511426.0</v>
       </c>
       <c r="N66" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O66" s="13" t="n">
-        <v>1.1331855E7</v>
+        <v>5893855.0</v>
       </c>
       <c r="P66" s="6" t="inlineStr">
         <is>
@@ -4342,12 +4330,12 @@
       </c>
       <c r="D67" s="7" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>39</t>
         </is>
       </c>
       <c r="E67" s="7" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>05/01/2026</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr">
@@ -4369,16 +4357,16 @@
       </c>
       <c r="K67" s="6"/>
       <c r="L67" s="13" t="n">
-        <v>6851048.0</v>
+        <v>4944615.0</v>
       </c>
       <c r="M67" s="13" t="n">
-        <v>680716.0</v>
+        <v>436294.0</v>
       </c>
       <c r="N67" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O67" s="13" t="n">
-        <v>7531764.0</v>
+        <v>5380909.0</v>
       </c>
       <c r="P67" s="6" t="inlineStr">
         <is>
@@ -4407,12 +4395,12 @@
       </c>
       <c r="D68" s="7" t="inlineStr">
         <is>
-          <t>65</t>
+          <t>4</t>
         </is>
       </c>
       <c r="E68" s="7" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr">
@@ -4434,16 +4422,16 @@
       </c>
       <c r="K68" s="6"/>
       <c r="L68" s="13" t="n">
-        <v>1.0702658E7</v>
+        <v>6936482.0</v>
       </c>
       <c r="M68" s="13" t="n">
-        <v>1006859.0</v>
+        <v>612501.0</v>
       </c>
       <c r="N68" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O68" s="13" t="n">
-        <v>1.1709517E7</v>
+        <v>7548983.0</v>
       </c>
       <c r="P68" s="6" t="inlineStr">
         <is>
@@ -4472,12 +4460,12 @@
       </c>
       <c r="D69" s="7" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>40</t>
         </is>
       </c>
       <c r="E69" s="7" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr">
@@ -4490,25 +4478,33 @@
           <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
-      <c r="H69" s="7"/>
-      <c r="I69" s="6"/>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>010175001031</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH VŨ THỊ HỒNG LOAN (NGỌC BẢO)</t>
+        </is>
+      </c>
       <c r="J69" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
+          <t>13 đường Bùi Thiện Ngộ, Phường Rạch Dừa, TP Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="K69" s="6"/>
       <c r="L69" s="13" t="n">
-        <v>5165235.0</v>
+        <v>6636350.0</v>
       </c>
       <c r="M69" s="13" t="n">
-        <v>452746.0</v>
+        <v>663635.0</v>
       </c>
       <c r="N69" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O69" s="13" t="n">
-        <v>5617981.0</v>
+        <v>7299985.0</v>
       </c>
       <c r="P69" s="6" t="inlineStr">
         <is>
@@ -4537,12 +4533,12 @@
       </c>
       <c r="D70" s="7" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>41</t>
         </is>
       </c>
       <c r="E70" s="7" t="inlineStr">
         <is>
-          <t>08/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">
@@ -4564,16 +4560,16 @@
       </c>
       <c r="K70" s="6"/>
       <c r="L70" s="13" t="n">
-        <v>1.1730015E7</v>
+        <v>5568181.0</v>
       </c>
       <c r="M70" s="13" t="n">
-        <v>1103336.0</v>
+        <v>545429.0</v>
       </c>
       <c r="N70" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O70" s="13" t="n">
-        <v>1.2833351E7</v>
+        <v>6113610.0</v>
       </c>
       <c r="P70" s="6" t="inlineStr">
         <is>
@@ -4602,12 +4598,12 @@
       </c>
       <c r="D71" s="7" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>42</t>
         </is>
       </c>
       <c r="E71" s="7" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr">
@@ -4622,23 +4618,19 @@
       </c>
       <c r="H71" s="7"/>
       <c r="I71" s="6"/>
-      <c r="J71" s="6" t="inlineStr">
-        <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
+      <c r="J71" s="6"/>
       <c r="K71" s="6"/>
       <c r="L71" s="13" t="n">
-        <v>1.2935204E7</v>
+        <v>2.67272E7</v>
       </c>
       <c r="M71" s="13" t="n">
-        <v>1289446.0</v>
+        <v>2672720.0</v>
       </c>
       <c r="N71" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O71" s="13" t="n">
-        <v>1.422465E7</v>
+        <v>2.939992E7</v>
       </c>
       <c r="P71" s="6" t="inlineStr">
         <is>
@@ -4667,12 +4659,12 @@
       </c>
       <c r="D72" s="7" t="inlineStr">
         <is>
-          <t>69</t>
+          <t>43</t>
         </is>
       </c>
       <c r="E72" s="7" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr">
@@ -4686,24 +4678,32 @@
         </is>
       </c>
       <c r="H72" s="7"/>
-      <c r="I72" s="6"/>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>268/15 Trần Phú</t>
+        </is>
+      </c>
       <c r="J72" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K72" s="6"/>
+          <t>268/15 Trần Phú , Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K72" s="6" t="inlineStr">
+        <is>
+          <t>087063018418</t>
+        </is>
+      </c>
       <c r="L72" s="13" t="n">
-        <v>4924446.0</v>
+        <v>3.4669524E7</v>
       </c>
       <c r="M72" s="13" t="n">
-        <v>409629.0</v>
+        <v>3385479.0</v>
       </c>
       <c r="N72" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O72" s="13" t="n">
-        <v>5334075.0</v>
+        <v>3.8055003E7</v>
       </c>
       <c r="P72" s="6" t="inlineStr">
         <is>
@@ -4732,12 +4732,12 @@
       </c>
       <c r="D73" s="7" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>44</t>
         </is>
       </c>
       <c r="E73" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr">
@@ -4751,24 +4751,32 @@
         </is>
       </c>
       <c r="H73" s="7"/>
-      <c r="I73" s="6"/>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>Trần Thanh Hưng</t>
+        </is>
+      </c>
       <c r="J73" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K73" s="6"/>
+          <t>507 B đường 2/9, Phường Rạch Dừa Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K73" s="6" t="inlineStr">
+        <is>
+          <t>052090000956</t>
+        </is>
+      </c>
       <c r="L73" s="13" t="n">
-        <v>2.67272E7</v>
+        <v>8072183.0</v>
       </c>
       <c r="M73" s="13" t="n">
-        <v>2672720.0</v>
+        <v>726721.0</v>
       </c>
       <c r="N73" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O73" s="13" t="n">
-        <v>2.939992E7</v>
+        <v>8798904.0</v>
       </c>
       <c r="P73" s="6" t="inlineStr">
         <is>
@@ -4797,12 +4805,12 @@
       </c>
       <c r="D74" s="7" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>45</t>
         </is>
       </c>
       <c r="E74" s="7" t="inlineStr">
         <is>
-          <t>09/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -4824,16 +4832,16 @@
       </c>
       <c r="K74" s="6"/>
       <c r="L74" s="13" t="n">
-        <v>5175861.0</v>
+        <v>1.153345E7</v>
       </c>
       <c r="M74" s="13" t="n">
-        <v>450789.0</v>
+        <v>1146234.0</v>
       </c>
       <c r="N74" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O74" s="13" t="n">
-        <v>5626650.0</v>
+        <v>1.2679684E7</v>
       </c>
       <c r="P74" s="6" t="inlineStr">
         <is>
@@ -4862,12 +4870,12 @@
       </c>
       <c r="D75" s="7" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>46</t>
         </is>
       </c>
       <c r="E75" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr">
@@ -4881,24 +4889,32 @@
         </is>
       </c>
       <c r="H75" s="7"/>
-      <c r="I75" s="6"/>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>NGUYỄN THỊ HẢI BÌNH</t>
+        </is>
+      </c>
       <c r="J75" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K75" s="6"/>
+          <t>199 Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K75" s="6" t="inlineStr">
+        <is>
+          <t>033189005308</t>
+        </is>
+      </c>
       <c r="L75" s="13" t="n">
-        <v>1.2758835E7</v>
+        <v>8792609.0</v>
       </c>
       <c r="M75" s="13" t="n">
-        <v>1236160.0</v>
+        <v>839465.0</v>
       </c>
       <c r="N75" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O75" s="13" t="n">
-        <v>1.3994995E7</v>
+        <v>9632074.0</v>
       </c>
       <c r="P75" s="6" t="inlineStr">
         <is>
@@ -4927,12 +4943,12 @@
       </c>
       <c r="D76" s="7" t="inlineStr">
         <is>
-          <t>72</t>
+          <t>47</t>
         </is>
       </c>
       <c r="E76" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>06/01/2026</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr">
@@ -4946,24 +4962,24 @@
         </is>
       </c>
       <c r="H76" s="7"/>
-      <c r="I76" s="6" t="inlineStr">
-        <is>
-          <t>Khách lẻ</t>
-        </is>
-      </c>
-      <c r="J76" s="6"/>
+      <c r="I76" s="6"/>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
       <c r="K76" s="6"/>
       <c r="L76" s="13" t="n">
-        <v>7935345.0</v>
+        <v>9664240.0</v>
       </c>
       <c r="M76" s="13" t="n">
-        <v>792700.0</v>
+        <v>961591.0</v>
       </c>
       <c r="N76" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O76" s="13" t="n">
-        <v>8728045.0</v>
+        <v>1.0625831E7</v>
       </c>
       <c r="P76" s="6" t="inlineStr">
         <is>
@@ -4992,12 +5008,12 @@
       </c>
       <c r="D77" s="7" t="inlineStr">
         <is>
-          <t>73</t>
+          <t>48</t>
         </is>
       </c>
       <c r="E77" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr">
@@ -5019,16 +5035,16 @@
       </c>
       <c r="K77" s="6"/>
       <c r="L77" s="13" t="n">
-        <v>9253872.0</v>
+        <v>5899396.0</v>
       </c>
       <c r="M77" s="13" t="n">
-        <v>916497.0</v>
+        <v>554088.0</v>
       </c>
       <c r="N77" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O77" s="13" t="n">
-        <v>1.0170369E7</v>
+        <v>6453484.0</v>
       </c>
       <c r="P77" s="6" t="inlineStr">
         <is>
@@ -5057,12 +5073,12 @@
       </c>
       <c r="D78" s="7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>49</t>
         </is>
       </c>
       <c r="E78" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr">
@@ -5076,24 +5092,32 @@
         </is>
       </c>
       <c r="H78" s="7"/>
-      <c r="I78" s="6"/>
+      <c r="I78" s="6" t="inlineStr">
+        <is>
+          <t>Cô Vân . 790 trần phú</t>
+        </is>
+      </c>
       <c r="J78" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K78" s="6"/>
+          <t>790 trần phú, Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K78" s="6" t="inlineStr">
+        <is>
+          <t>075159002802</t>
+        </is>
+      </c>
       <c r="L78" s="13" t="n">
-        <v>1.0491413E7</v>
+        <v>3314238.0</v>
       </c>
       <c r="M78" s="13" t="n">
-        <v>981086.0</v>
+        <v>312720.0</v>
       </c>
       <c r="N78" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O78" s="13" t="n">
-        <v>1.1472499E7</v>
+        <v>3626958.0</v>
       </c>
       <c r="P78" s="6" t="inlineStr">
         <is>
@@ -5122,12 +5146,12 @@
       </c>
       <c r="D79" s="7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E79" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr">
@@ -5144,21 +5168,25 @@
       <c r="I79" s="6"/>
       <c r="J79" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K79" s="6"/>
+          <t>1507/2 A Đường 30/4 Phường Phước Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K79" s="6" t="inlineStr">
+        <is>
+          <t>077096003835</t>
+        </is>
+      </c>
       <c r="L79" s="13" t="n">
-        <v>1.0680423E7</v>
+        <v>8122536.0</v>
       </c>
       <c r="M79" s="13" t="n">
-        <v>1025117.0</v>
+        <v>748462.0</v>
       </c>
       <c r="N79" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O79" s="13" t="n">
-        <v>1.170554E7</v>
+        <v>8870998.0</v>
       </c>
       <c r="P79" s="6" t="inlineStr">
         <is>
@@ -5187,12 +5215,12 @@
       </c>
       <c r="D80" s="7" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>50</t>
         </is>
       </c>
       <c r="E80" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr">
@@ -5206,24 +5234,24 @@
         </is>
       </c>
       <c r="H80" s="7"/>
-      <c r="I80" s="6" t="inlineStr">
-        <is>
-          <t>Khách lẻ</t>
-        </is>
-      </c>
-      <c r="J80" s="6"/>
+      <c r="I80" s="6"/>
+      <c r="J80" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
       <c r="K80" s="6"/>
       <c r="L80" s="13" t="n">
-        <v>1.2567115E7</v>
+        <v>1.0153298E7</v>
       </c>
       <c r="M80" s="13" t="n">
-        <v>1182824.0</v>
+        <v>998237.0</v>
       </c>
       <c r="N80" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O80" s="13" t="n">
-        <v>1.3749939E7</v>
+        <v>1.1151535E7</v>
       </c>
       <c r="P80" s="6" t="inlineStr">
         <is>
@@ -5252,12 +5280,12 @@
       </c>
       <c r="D81" s="7" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>51</t>
         </is>
       </c>
       <c r="E81" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr">
@@ -5279,16 +5307,16 @@
       </c>
       <c r="K81" s="6"/>
       <c r="L81" s="13" t="n">
-        <v>6555870.0</v>
+        <v>5879236.0</v>
       </c>
       <c r="M81" s="13" t="n">
-        <v>600569.0</v>
+        <v>543793.0</v>
       </c>
       <c r="N81" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O81" s="13" t="n">
-        <v>7156439.0</v>
+        <v>6423029.0</v>
       </c>
       <c r="P81" s="6" t="inlineStr">
         <is>
@@ -5317,12 +5345,12 @@
       </c>
       <c r="D82" s="7" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>52</t>
         </is>
       </c>
       <c r="E82" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr">
@@ -5339,21 +5367,25 @@
       <c r="I82" s="6"/>
       <c r="J82" s="6" t="inlineStr">
         <is>
-          <t>khách lẻ không lấy hóa đơn</t>
-        </is>
-      </c>
-      <c r="K82" s="6"/>
+          <t>118 Nguyễn Văn Trỗi Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K82" s="6" t="inlineStr">
+        <is>
+          <t>077166000908</t>
+        </is>
+      </c>
       <c r="L82" s="13" t="n">
-        <v>7410648.0</v>
+        <v>8333944.0</v>
       </c>
       <c r="M82" s="13" t="n">
-        <v>684063.0</v>
+        <v>772875.0</v>
       </c>
       <c r="N82" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O82" s="13" t="n">
-        <v>8094711.0</v>
+        <v>9106819.0</v>
       </c>
       <c r="P82" s="6" t="inlineStr">
         <is>
@@ -5382,12 +5414,12 @@
       </c>
       <c r="D83" s="7" t="inlineStr">
         <is>
-          <t>79</t>
+          <t>53</t>
         </is>
       </c>
       <c r="E83" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr">
@@ -5403,22 +5435,30 @@
       <c r="H83" s="7"/>
       <c r="I83" s="6" t="inlineStr">
         <is>
-          <t>Khách lẻ</t>
-        </is>
-      </c>
-      <c r="J83" s="6"/>
-      <c r="K83" s="6"/>
+          <t>Nguyễn Thị Ngọc Châu</t>
+        </is>
+      </c>
+      <c r="J83" s="6" t="inlineStr">
+        <is>
+          <t>61/2/1 Nguyễn An Ninh, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K83" s="6" t="inlineStr">
+        <is>
+          <t>077190007452</t>
+        </is>
+      </c>
       <c r="L83" s="13" t="n">
-        <v>9203430.0</v>
+        <v>7741616.0</v>
       </c>
       <c r="M83" s="13" t="n">
-        <v>908213.0</v>
+        <v>742717.0</v>
       </c>
       <c r="N83" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O83" s="13" t="n">
-        <v>1.0111643E7</v>
+        <v>8484333.0</v>
       </c>
       <c r="P83" s="6" t="inlineStr">
         <is>
@@ -5447,12 +5487,12 @@
       </c>
       <c r="D84" s="7" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>54</t>
         </is>
       </c>
       <c r="E84" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr">
@@ -5474,16 +5514,16 @@
       </c>
       <c r="K84" s="6"/>
       <c r="L84" s="13" t="n">
-        <v>4.72728E7</v>
+        <v>1.0576309E7</v>
       </c>
       <c r="M84" s="13" t="n">
-        <v>4727280.0</v>
+        <v>981057.0</v>
       </c>
       <c r="N84" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O84" s="13" t="n">
-        <v>5.200008E7</v>
+        <v>1.1557366E7</v>
       </c>
       <c r="P84" s="6" t="inlineStr">
         <is>
@@ -5512,12 +5552,12 @@
       </c>
       <c r="D85" s="7" t="inlineStr">
         <is>
-          <t>80</t>
+          <t>55</t>
         </is>
       </c>
       <c r="E85" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr">
@@ -5539,16 +5579,16 @@
       </c>
       <c r="K85" s="6"/>
       <c r="L85" s="13" t="n">
-        <v>1.0934856E7</v>
+        <v>8964622.0</v>
       </c>
       <c r="M85" s="13" t="n">
-        <v>1093486.0</v>
+        <v>859241.0</v>
       </c>
       <c r="N85" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O85" s="13" t="n">
-        <v>1.2028342E7</v>
+        <v>9823863.0</v>
       </c>
       <c r="P85" s="6" t="inlineStr">
         <is>
@@ -5577,12 +5617,12 @@
       </c>
       <c r="D86" s="7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>56</t>
         </is>
       </c>
       <c r="E86" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr">
@@ -5604,16 +5644,16 @@
       </c>
       <c r="K86" s="6"/>
       <c r="L86" s="13" t="n">
-        <v>6678910.0</v>
+        <v>8861692.0</v>
       </c>
       <c r="M86" s="13" t="n">
-        <v>567039.0</v>
+        <v>731874.0</v>
       </c>
       <c r="N86" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O86" s="13" t="n">
-        <v>7245949.0</v>
+        <v>9593566.0</v>
       </c>
       <c r="P86" s="6" t="inlineStr">
         <is>
@@ -5642,12 +5682,12 @@
       </c>
       <c r="D87" s="7" t="inlineStr">
         <is>
-          <t>82</t>
+          <t>57</t>
         </is>
       </c>
       <c r="E87" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr">
@@ -5669,16 +5709,16 @@
       </c>
       <c r="K87" s="6"/>
       <c r="L87" s="13" t="n">
-        <v>7595905.0</v>
+        <v>4638895.0</v>
       </c>
       <c r="M87" s="13" t="n">
-        <v>649128.0</v>
+        <v>371110.0</v>
       </c>
       <c r="N87" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O87" s="13" t="n">
-        <v>8245033.0</v>
+        <v>5010005.0</v>
       </c>
       <c r="P87" s="6" t="inlineStr">
         <is>
@@ -5707,12 +5747,12 @@
       </c>
       <c r="D88" s="7" t="inlineStr">
         <is>
-          <t>83</t>
+          <t>58</t>
         </is>
       </c>
       <c r="E88" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr">
@@ -5734,16 +5774,16 @@
       </c>
       <c r="K88" s="6"/>
       <c r="L88" s="13" t="n">
-        <v>1.0127228E7</v>
+        <v>8367763.0</v>
       </c>
       <c r="M88" s="13" t="n">
-        <v>904724.0</v>
+        <v>829758.0</v>
       </c>
       <c r="N88" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O88" s="13" t="n">
-        <v>1.1031952E7</v>
+        <v>9197521.0</v>
       </c>
       <c r="P88" s="6" t="inlineStr">
         <is>
@@ -5772,12 +5812,12 @@
       </c>
       <c r="D89" s="7" t="inlineStr">
         <is>
-          <t>84</t>
+          <t>59</t>
         </is>
       </c>
       <c r="E89" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>07/01/2026</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr">
@@ -5799,16 +5839,16 @@
       </c>
       <c r="K89" s="6"/>
       <c r="L89" s="13" t="n">
-        <v>5224214.0</v>
+        <v>8181800.0</v>
       </c>
       <c r="M89" s="13" t="n">
-        <v>445311.0</v>
+        <v>818180.0</v>
       </c>
       <c r="N89" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O89" s="13" t="n">
-        <v>5669525.0</v>
+        <v>8999980.0</v>
       </c>
       <c r="P89" s="6" t="inlineStr">
         <is>
@@ -5837,12 +5877,12 @@
       </c>
       <c r="D90" s="7" t="inlineStr">
         <is>
-          <t>85</t>
+          <t>6</t>
         </is>
       </c>
       <c r="E90" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr">
@@ -5864,16 +5904,16 @@
       </c>
       <c r="K90" s="6"/>
       <c r="L90" s="13" t="n">
-        <v>9419615.0</v>
+        <v>7901852.0</v>
       </c>
       <c r="M90" s="13" t="n">
-        <v>825387.0</v>
+        <v>687168.0</v>
       </c>
       <c r="N90" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O90" s="13" t="n">
-        <v>1.0245002E7</v>
+        <v>8589020.0</v>
       </c>
       <c r="P90" s="6" t="inlineStr">
         <is>
@@ -5902,12 +5942,12 @@
       </c>
       <c r="D91" s="7" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>60</t>
         </is>
       </c>
       <c r="E91" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr">
@@ -5929,16 +5969,16 @@
       </c>
       <c r="K91" s="6"/>
       <c r="L91" s="13" t="n">
-        <v>8100700.0</v>
+        <v>7954452.0</v>
       </c>
       <c r="M91" s="13" t="n">
-        <v>678966.0</v>
+        <v>791371.0</v>
       </c>
       <c r="N91" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O91" s="13" t="n">
-        <v>8779666.0</v>
+        <v>8745823.0</v>
       </c>
       <c r="P91" s="6" t="inlineStr">
         <is>
@@ -5967,12 +6007,12 @@
       </c>
       <c r="D92" s="7" t="inlineStr">
         <is>
-          <t>87</t>
+          <t>61</t>
         </is>
       </c>
       <c r="E92" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr">
@@ -5994,16 +6034,16 @@
       </c>
       <c r="K92" s="6"/>
       <c r="L92" s="13" t="n">
-        <v>8901234.0</v>
+        <v>8974728.0</v>
       </c>
       <c r="M92" s="13" t="n">
-        <v>862195.0</v>
+        <v>788888.0</v>
       </c>
       <c r="N92" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O92" s="13" t="n">
-        <v>9763429.0</v>
+        <v>9763616.0</v>
       </c>
       <c r="P92" s="6" t="inlineStr">
         <is>
@@ -6032,12 +6072,12 @@
       </c>
       <c r="D93" s="7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>62</t>
         </is>
       </c>
       <c r="E93" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr">
@@ -6051,32 +6091,24 @@
         </is>
       </c>
       <c r="H93" s="7"/>
-      <c r="I93" s="6" t="inlineStr">
-        <is>
-          <t>NGUYỄN THỊ HẢI BÌNH</t>
-        </is>
-      </c>
+      <c r="I93" s="6"/>
       <c r="J93" s="6" t="inlineStr">
         <is>
-          <t>199 Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K93" s="6" t="inlineStr">
-        <is>
-          <t>033189005308</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K93" s="6"/>
       <c r="L93" s="13" t="n">
-        <v>3389233.0</v>
+        <v>7212866.0</v>
       </c>
       <c r="M93" s="13" t="n">
-        <v>297220.0</v>
+        <v>689529.0</v>
       </c>
       <c r="N93" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O93" s="13" t="n">
-        <v>3686453.0</v>
+        <v>7902395.0</v>
       </c>
       <c r="P93" s="6" t="inlineStr">
         <is>
@@ -6105,12 +6137,12 @@
       </c>
       <c r="D94" s="7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>63</t>
         </is>
       </c>
       <c r="E94" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr">
@@ -6124,32 +6156,24 @@
         </is>
       </c>
       <c r="H94" s="7"/>
-      <c r="I94" s="6" t="inlineStr">
-        <is>
-          <t>Trần Thanh Hưng</t>
-        </is>
-      </c>
+      <c r="I94" s="6"/>
       <c r="J94" s="6" t="inlineStr">
         <is>
-          <t>507 B đường 2/9, Phường Rạch Dừa Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K94" s="6" t="inlineStr">
-        <is>
-          <t>052090000956</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K94" s="6"/>
       <c r="L94" s="13" t="n">
-        <v>2702706.0</v>
+        <v>1.0307579E7</v>
       </c>
       <c r="M94" s="13" t="n">
-        <v>244289.0</v>
+        <v>1024276.0</v>
       </c>
       <c r="N94" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O94" s="13" t="n">
-        <v>2946995.0</v>
+        <v>1.1331855E7</v>
       </c>
       <c r="P94" s="6" t="inlineStr">
         <is>
@@ -6178,12 +6202,12 @@
       </c>
       <c r="D95" s="7" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>64</t>
         </is>
       </c>
       <c r="E95" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr">
@@ -6197,32 +6221,24 @@
         </is>
       </c>
       <c r="H95" s="7"/>
-      <c r="I95" s="6" t="inlineStr">
-        <is>
-          <t>Phạm Thị Trúc Mai</t>
-        </is>
-      </c>
+      <c r="I95" s="6"/>
       <c r="J95" s="6" t="inlineStr">
         <is>
-          <t>34/11 A Lương Văn Can Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K95" s="6" t="inlineStr">
-        <is>
-          <t>086185004284</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K95" s="6"/>
       <c r="L95" s="13" t="n">
-        <v>7325388.0</v>
+        <v>6851048.0</v>
       </c>
       <c r="M95" s="13" t="n">
-        <v>689632.0</v>
+        <v>680716.0</v>
       </c>
       <c r="N95" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O95" s="13" t="n">
-        <v>8015020.0</v>
+        <v>7531764.0</v>
       </c>
       <c r="P95" s="6" t="inlineStr">
         <is>
@@ -6251,12 +6267,12 @@
       </c>
       <c r="D96" s="7" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>65</t>
         </is>
       </c>
       <c r="E96" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr">
@@ -6278,16 +6294,16 @@
       </c>
       <c r="K96" s="6"/>
       <c r="L96" s="13" t="n">
-        <v>8943696.0</v>
+        <v>1.0702658E7</v>
       </c>
       <c r="M96" s="13" t="n">
-        <v>868221.0</v>
+        <v>1006859.0</v>
       </c>
       <c r="N96" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O96" s="13" t="n">
-        <v>9811917.0</v>
+        <v>1.1709517E7</v>
       </c>
       <c r="P96" s="6" t="inlineStr">
         <is>
@@ -6316,12 +6332,12 @@
       </c>
       <c r="D97" s="7" t="inlineStr">
         <is>
-          <t>91</t>
+          <t>66</t>
         </is>
       </c>
       <c r="E97" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr">
@@ -6338,25 +6354,21 @@
       <c r="I97" s="6"/>
       <c r="J97" s="6" t="inlineStr">
         <is>
-          <t>135/2 C LÊ QUANG ĐỊNH PHƯỜNG RẠCH DỪA THÀNH PHỐ HỒ CHÍ MINH</t>
-        </is>
-      </c>
-      <c r="K97" s="6" t="inlineStr">
-        <is>
-          <t>077194008987</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K97" s="6"/>
       <c r="L97" s="13" t="n">
-        <v>3498983.0</v>
+        <v>5165235.0</v>
       </c>
       <c r="M97" s="13" t="n">
-        <v>289082.0</v>
+        <v>452746.0</v>
       </c>
       <c r="N97" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O97" s="13" t="n">
-        <v>3788065.0</v>
+        <v>5617981.0</v>
       </c>
       <c r="P97" s="6" t="inlineStr">
         <is>
@@ -6385,12 +6397,12 @@
       </c>
       <c r="D98" s="7" t="inlineStr">
         <is>
-          <t>92</t>
+          <t>67</t>
         </is>
       </c>
       <c r="E98" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>08/01/2026</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr">
@@ -6404,32 +6416,24 @@
         </is>
       </c>
       <c r="H98" s="7"/>
-      <c r="I98" s="6" t="inlineStr">
-        <is>
-          <t>Cô Vân . 790 trần phú</t>
-        </is>
-      </c>
+      <c r="I98" s="6"/>
       <c r="J98" s="6" t="inlineStr">
         <is>
-          <t>790 trần phú, Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
-        </is>
-      </c>
-      <c r="K98" s="6" t="inlineStr">
-        <is>
-          <t>075159002802</t>
-        </is>
-      </c>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K98" s="6"/>
       <c r="L98" s="13" t="n">
-        <v>4797624.0</v>
+        <v>1.1730015E7</v>
       </c>
       <c r="M98" s="13" t="n">
-        <v>448689.0</v>
+        <v>1103336.0</v>
       </c>
       <c r="N98" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O98" s="13" t="n">
-        <v>5246313.0</v>
+        <v>1.2833351E7</v>
       </c>
       <c r="P98" s="6" t="inlineStr">
         <is>
@@ -6458,12 +6462,12 @@
       </c>
       <c r="D99" s="7" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>68</t>
         </is>
       </c>
       <c r="E99" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr">
@@ -6485,16 +6489,16 @@
       </c>
       <c r="K99" s="6"/>
       <c r="L99" s="13" t="n">
-        <v>1.0657357E7</v>
+        <v>1.2935204E7</v>
       </c>
       <c r="M99" s="13" t="n">
-        <v>1025737.0</v>
+        <v>1289446.0</v>
       </c>
       <c r="N99" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O99" s="13" t="n">
-        <v>1.1683094E7</v>
+        <v>1.422465E7</v>
       </c>
       <c r="P99" s="6" t="inlineStr">
         <is>
@@ -6523,12 +6527,12 @@
       </c>
       <c r="D100" s="7" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>69</t>
         </is>
       </c>
       <c r="E100" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>09/01/2026</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr">
@@ -6541,33 +6545,25 @@
           <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
-      <c r="H100" s="7" t="inlineStr">
-        <is>
-          <t>3502556808</t>
-        </is>
-      </c>
-      <c r="I100" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THƯƠNG MẠI THỦY HẢI SẢN KIM NGÂN</t>
-        </is>
-      </c>
+      <c r="H100" s="7"/>
+      <c r="I100" s="6"/>
       <c r="J100" s="6" t="inlineStr">
         <is>
-          <t>Số 65A Yên Bái, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+          <t>khách lẻ không lấy hóa đơn</t>
         </is>
       </c>
       <c r="K100" s="6"/>
       <c r="L100" s="13" t="n">
-        <v>8499975.0</v>
+        <v>4924446.0</v>
       </c>
       <c r="M100" s="13" t="n">
-        <v>849998.0</v>
+        <v>409629.0</v>
       </c>
       <c r="N100" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O100" s="13" t="n">
-        <v>9349973.0</v>
+        <v>5334075.0</v>
       </c>
       <c r="P100" s="6" t="inlineStr">
         <is>
@@ -6596,12 +6592,12 @@
       </c>
       <c r="D101" s="7" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E101" s="7" t="inlineStr">
         <is>
-          <t>10/01/2026</t>
+          <t>02/01/2026</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr">
@@ -6614,40 +6610,2164 @@
           <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
         </is>
       </c>
-      <c r="H101" s="7" t="inlineStr">
-        <is>
-          <t>077088009229</t>
-        </is>
-      </c>
-      <c r="I101" s="6" t="inlineStr">
-        <is>
-          <t>HỘ KINH DOANH TÂM NGUYỄN (DƯƠNG THẾ HUY)</t>
-        </is>
-      </c>
+      <c r="H101" s="7"/>
+      <c r="I101" s="6"/>
       <c r="J101" s="6" t="inlineStr">
         <is>
-          <t>04 đường Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+          <t>khách lẻ không lấy hóa đơn</t>
         </is>
       </c>
       <c r="K101" s="6"/>
       <c r="L101" s="13" t="n">
+        <v>2.67272E7</v>
+      </c>
+      <c r="M101" s="13" t="n">
+        <v>2672720.0</v>
+      </c>
+      <c r="N101" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O101" s="13" t="n">
+        <v>2.939992E7</v>
+      </c>
+      <c r="P101" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q101" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>96.0</v>
+      </c>
+      <c r="B102" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="E102" s="7" t="inlineStr">
+        <is>
+          <t>09/01/2026</t>
+        </is>
+      </c>
+      <c r="F102" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G102" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H102" s="7"/>
+      <c r="I102" s="6"/>
+      <c r="J102" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K102" s="6"/>
+      <c r="L102" s="13" t="n">
+        <v>5175861.0</v>
+      </c>
+      <c r="M102" s="13" t="n">
+        <v>450789.0</v>
+      </c>
+      <c r="N102" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O102" s="13" t="n">
+        <v>5626650.0</v>
+      </c>
+      <c r="P102" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q102" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>97.0</v>
+      </c>
+      <c r="B103" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C103" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D103" s="7" t="inlineStr">
+        <is>
+          <t>71</t>
+        </is>
+      </c>
+      <c r="E103" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F103" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G103" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H103" s="7"/>
+      <c r="I103" s="6"/>
+      <c r="J103" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K103" s="6"/>
+      <c r="L103" s="13" t="n">
+        <v>1.2758835E7</v>
+      </c>
+      <c r="M103" s="13" t="n">
+        <v>1236160.0</v>
+      </c>
+      <c r="N103" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O103" s="13" t="n">
+        <v>1.3994995E7</v>
+      </c>
+      <c r="P103" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q103" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>98.0</v>
+      </c>
+      <c r="B104" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C104" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D104" s="7" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="E104" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F104" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G104" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H104" s="7"/>
+      <c r="I104" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J104" s="6"/>
+      <c r="K104" s="6"/>
+      <c r="L104" s="13" t="n">
+        <v>7935345.0</v>
+      </c>
+      <c r="M104" s="13" t="n">
+        <v>792700.0</v>
+      </c>
+      <c r="N104" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O104" s="13" t="n">
+        <v>8728045.0</v>
+      </c>
+      <c r="P104" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q104" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>99.0</v>
+      </c>
+      <c r="B105" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C105" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D105" s="7" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E105" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F105" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G105" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H105" s="7"/>
+      <c r="I105" s="6"/>
+      <c r="J105" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K105" s="6"/>
+      <c r="L105" s="13" t="n">
+        <v>9253872.0</v>
+      </c>
+      <c r="M105" s="13" t="n">
+        <v>916497.0</v>
+      </c>
+      <c r="N105" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O105" s="13" t="n">
+        <v>1.0170369E7</v>
+      </c>
+      <c r="P105" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q105" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>100.0</v>
+      </c>
+      <c r="B106" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C106" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D106" s="7" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E106" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F106" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H106" s="7"/>
+      <c r="I106" s="6"/>
+      <c r="J106" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K106" s="6"/>
+      <c r="L106" s="13" t="n">
+        <v>1.0491413E7</v>
+      </c>
+      <c r="M106" s="13" t="n">
+        <v>981086.0</v>
+      </c>
+      <c r="N106" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O106" s="13" t="n">
+        <v>1.1472499E7</v>
+      </c>
+      <c r="P106" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q106" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>101.0</v>
+      </c>
+      <c r="B107" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C107" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D107" s="7" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="E107" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G107" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H107" s="7"/>
+      <c r="I107" s="6"/>
+      <c r="J107" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K107" s="6"/>
+      <c r="L107" s="13" t="n">
+        <v>1.0680423E7</v>
+      </c>
+      <c r="M107" s="13" t="n">
+        <v>1025117.0</v>
+      </c>
+      <c r="N107" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O107" s="13" t="n">
+        <v>1.170554E7</v>
+      </c>
+      <c r="P107" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q107" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>102.0</v>
+      </c>
+      <c r="B108" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C108" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D108" s="7" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E108" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F108" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H108" s="7"/>
+      <c r="I108" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J108" s="6"/>
+      <c r="K108" s="6"/>
+      <c r="L108" s="13" t="n">
+        <v>1.2567115E7</v>
+      </c>
+      <c r="M108" s="13" t="n">
+        <v>1182824.0</v>
+      </c>
+      <c r="N108" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O108" s="13" t="n">
+        <v>1.3749939E7</v>
+      </c>
+      <c r="P108" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q108" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>103.0</v>
+      </c>
+      <c r="B109" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C109" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D109" s="7" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+      <c r="E109" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F109" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G109" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H109" s="7"/>
+      <c r="I109" s="6"/>
+      <c r="J109" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K109" s="6"/>
+      <c r="L109" s="13" t="n">
+        <v>6555870.0</v>
+      </c>
+      <c r="M109" s="13" t="n">
+        <v>600569.0</v>
+      </c>
+      <c r="N109" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O109" s="13" t="n">
+        <v>7156439.0</v>
+      </c>
+      <c r="P109" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q109" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n">
+        <v>104.0</v>
+      </c>
+      <c r="B110" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D110" s="7" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="E110" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F110" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H110" s="7"/>
+      <c r="I110" s="6"/>
+      <c r="J110" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K110" s="6"/>
+      <c r="L110" s="13" t="n">
+        <v>7410648.0</v>
+      </c>
+      <c r="M110" s="13" t="n">
+        <v>684063.0</v>
+      </c>
+      <c r="N110" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O110" s="13" t="n">
+        <v>8094711.0</v>
+      </c>
+      <c r="P110" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q110" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>105.0</v>
+      </c>
+      <c r="B111" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C111" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D111" s="7" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="E111" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F111" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G111" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H111" s="7"/>
+      <c r="I111" s="6" t="inlineStr">
+        <is>
+          <t>Khách lẻ</t>
+        </is>
+      </c>
+      <c r="J111" s="6"/>
+      <c r="K111" s="6"/>
+      <c r="L111" s="13" t="n">
+        <v>9203430.0</v>
+      </c>
+      <c r="M111" s="13" t="n">
+        <v>908213.0</v>
+      </c>
+      <c r="N111" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O111" s="13" t="n">
+        <v>1.0111643E7</v>
+      </c>
+      <c r="P111" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q111" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>106.0</v>
+      </c>
+      <c r="B112" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C112" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D112" s="7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E112" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F112" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H112" s="7"/>
+      <c r="I112" s="6"/>
+      <c r="J112" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K112" s="6"/>
+      <c r="L112" s="13" t="n">
+        <v>4.72728E7</v>
+      </c>
+      <c r="M112" s="13" t="n">
+        <v>4727280.0</v>
+      </c>
+      <c r="N112" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O112" s="13" t="n">
+        <v>5.200008E7</v>
+      </c>
+      <c r="P112" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q112" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>107.0</v>
+      </c>
+      <c r="B113" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C113" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D113" s="7" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="E113" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F113" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G113" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H113" s="7"/>
+      <c r="I113" s="6"/>
+      <c r="J113" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K113" s="6"/>
+      <c r="L113" s="13" t="n">
+        <v>1.0934856E7</v>
+      </c>
+      <c r="M113" s="13" t="n">
+        <v>1093486.0</v>
+      </c>
+      <c r="N113" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O113" s="13" t="n">
+        <v>1.2028342E7</v>
+      </c>
+      <c r="P113" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q113" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>108.0</v>
+      </c>
+      <c r="B114" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C114" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D114" s="7" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="E114" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F114" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H114" s="7"/>
+      <c r="I114" s="6"/>
+      <c r="J114" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K114" s="6"/>
+      <c r="L114" s="13" t="n">
+        <v>6678910.0</v>
+      </c>
+      <c r="M114" s="13" t="n">
+        <v>567039.0</v>
+      </c>
+      <c r="N114" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O114" s="13" t="n">
+        <v>7245949.0</v>
+      </c>
+      <c r="P114" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q114" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>109.0</v>
+      </c>
+      <c r="B115" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D115" s="7" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="E115" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F115" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G115" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H115" s="7"/>
+      <c r="I115" s="6"/>
+      <c r="J115" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K115" s="6"/>
+      <c r="L115" s="13" t="n">
+        <v>7595905.0</v>
+      </c>
+      <c r="M115" s="13" t="n">
+        <v>649128.0</v>
+      </c>
+      <c r="N115" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O115" s="13" t="n">
+        <v>8245033.0</v>
+      </c>
+      <c r="P115" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q115" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>110.0</v>
+      </c>
+      <c r="B116" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C116" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D116" s="7" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="E116" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F116" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G116" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H116" s="7"/>
+      <c r="I116" s="6"/>
+      <c r="J116" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K116" s="6"/>
+      <c r="L116" s="13" t="n">
+        <v>1.0127228E7</v>
+      </c>
+      <c r="M116" s="13" t="n">
+        <v>904724.0</v>
+      </c>
+      <c r="N116" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O116" s="13" t="n">
+        <v>1.1031952E7</v>
+      </c>
+      <c r="P116" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q116" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="4" t="n">
+        <v>111.0</v>
+      </c>
+      <c r="B117" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D117" s="7" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="E117" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F117" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G117" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H117" s="7"/>
+      <c r="I117" s="6"/>
+      <c r="J117" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K117" s="6"/>
+      <c r="L117" s="13" t="n">
+        <v>5224214.0</v>
+      </c>
+      <c r="M117" s="13" t="n">
+        <v>445311.0</v>
+      </c>
+      <c r="N117" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O117" s="13" t="n">
+        <v>5669525.0</v>
+      </c>
+      <c r="P117" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q117" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="4" t="n">
+        <v>112.0</v>
+      </c>
+      <c r="B118" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C118" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D118" s="7" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E118" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F118" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G118" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H118" s="7"/>
+      <c r="I118" s="6"/>
+      <c r="J118" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K118" s="6"/>
+      <c r="L118" s="13" t="n">
+        <v>9419615.0</v>
+      </c>
+      <c r="M118" s="13" t="n">
+        <v>825387.0</v>
+      </c>
+      <c r="N118" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O118" s="13" t="n">
+        <v>1.0245002E7</v>
+      </c>
+      <c r="P118" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q118" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="4" t="n">
+        <v>113.0</v>
+      </c>
+      <c r="B119" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C119" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D119" s="7" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="E119" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F119" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G119" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H119" s="7"/>
+      <c r="I119" s="6"/>
+      <c r="J119" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K119" s="6"/>
+      <c r="L119" s="13" t="n">
+        <v>8100700.0</v>
+      </c>
+      <c r="M119" s="13" t="n">
+        <v>678966.0</v>
+      </c>
+      <c r="N119" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O119" s="13" t="n">
+        <v>8779666.0</v>
+      </c>
+      <c r="P119" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q119" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="4" t="n">
+        <v>114.0</v>
+      </c>
+      <c r="B120" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D120" s="7" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+      <c r="E120" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F120" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G120" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H120" s="7"/>
+      <c r="I120" s="6"/>
+      <c r="J120" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K120" s="6"/>
+      <c r="L120" s="13" t="n">
+        <v>8901234.0</v>
+      </c>
+      <c r="M120" s="13" t="n">
+        <v>862195.0</v>
+      </c>
+      <c r="N120" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O120" s="13" t="n">
+        <v>9763429.0</v>
+      </c>
+      <c r="P120" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q120" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="4" t="n">
+        <v>115.0</v>
+      </c>
+      <c r="B121" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D121" s="7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="E121" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F121" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H121" s="7"/>
+      <c r="I121" s="6" t="inlineStr">
+        <is>
+          <t>NGUYỄN THỊ HẢI BÌNH</t>
+        </is>
+      </c>
+      <c r="J121" s="6" t="inlineStr">
+        <is>
+          <t>199 Nam Kỳ Khởi Nghĩa, Phường Vũng Tàu, Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K121" s="6" t="inlineStr">
+        <is>
+          <t>033189005308</t>
+        </is>
+      </c>
+      <c r="L121" s="13" t="n">
+        <v>3389233.0</v>
+      </c>
+      <c r="M121" s="13" t="n">
+        <v>297220.0</v>
+      </c>
+      <c r="N121" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O121" s="13" t="n">
+        <v>3686453.0</v>
+      </c>
+      <c r="P121" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q121" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="4" t="n">
+        <v>116.0</v>
+      </c>
+      <c r="B122" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D122" s="7" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="E122" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F122" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G122" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H122" s="7"/>
+      <c r="I122" s="6" t="inlineStr">
+        <is>
+          <t>Trần Thanh Hưng</t>
+        </is>
+      </c>
+      <c r="J122" s="6" t="inlineStr">
+        <is>
+          <t>507 B đường 2/9, Phường Rạch Dừa Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K122" s="6" t="inlineStr">
+        <is>
+          <t>052090000956</t>
+        </is>
+      </c>
+      <c r="L122" s="13" t="n">
+        <v>2702706.0</v>
+      </c>
+      <c r="M122" s="13" t="n">
+        <v>244289.0</v>
+      </c>
+      <c r="N122" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O122" s="13" t="n">
+        <v>2946995.0</v>
+      </c>
+      <c r="P122" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q122" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="4" t="n">
+        <v>117.0</v>
+      </c>
+      <c r="B123" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C123" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D123" s="7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="E123" s="7" t="inlineStr">
+        <is>
+          <t>02/01/2026</t>
+        </is>
+      </c>
+      <c r="F123" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H123" s="7"/>
+      <c r="I123" s="6" t="inlineStr">
+        <is>
+          <t>Phạm Thị Trúc Mai</t>
+        </is>
+      </c>
+      <c r="J123" s="6" t="inlineStr">
+        <is>
+          <t>34/11 A Lương Văn Can Phường Tam Thắng Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K123" s="6" t="inlineStr">
+        <is>
+          <t>086185004284</t>
+        </is>
+      </c>
+      <c r="L123" s="13" t="n">
+        <v>7325388.0</v>
+      </c>
+      <c r="M123" s="13" t="n">
+        <v>689632.0</v>
+      </c>
+      <c r="N123" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O123" s="13" t="n">
+        <v>8015020.0</v>
+      </c>
+      <c r="P123" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q123" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="4" t="n">
+        <v>118.0</v>
+      </c>
+      <c r="B124" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C124" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D124" s="7" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="E124" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F124" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G124" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H124" s="7"/>
+      <c r="I124" s="6"/>
+      <c r="J124" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K124" s="6"/>
+      <c r="L124" s="13" t="n">
+        <v>8943696.0</v>
+      </c>
+      <c r="M124" s="13" t="n">
+        <v>868221.0</v>
+      </c>
+      <c r="N124" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O124" s="13" t="n">
+        <v>9811917.0</v>
+      </c>
+      <c r="P124" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q124" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="4" t="n">
+        <v>119.0</v>
+      </c>
+      <c r="B125" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C125" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D125" s="7" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="E125" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F125" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H125" s="7"/>
+      <c r="I125" s="6"/>
+      <c r="J125" s="6" t="inlineStr">
+        <is>
+          <t>135/2 C LÊ QUANG ĐỊNH PHƯỜNG RẠCH DỪA THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="K125" s="6" t="inlineStr">
+        <is>
+          <t>077194008987</t>
+        </is>
+      </c>
+      <c r="L125" s="13" t="n">
+        <v>3498983.0</v>
+      </c>
+      <c r="M125" s="13" t="n">
+        <v>289082.0</v>
+      </c>
+      <c r="N125" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O125" s="13" t="n">
+        <v>3788065.0</v>
+      </c>
+      <c r="P125" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q125" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="4" t="n">
+        <v>120.0</v>
+      </c>
+      <c r="B126" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C126" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D126" s="7" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="E126" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F126" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H126" s="7"/>
+      <c r="I126" s="6" t="inlineStr">
+        <is>
+          <t>Cô Vân . 790 trần phú</t>
+        </is>
+      </c>
+      <c r="J126" s="6" t="inlineStr">
+        <is>
+          <t>790 trần phú, Phường Vũng Tàu Thành Phố Hồ Chí Minh</t>
+        </is>
+      </c>
+      <c r="K126" s="6" t="inlineStr">
+        <is>
+          <t>075159002802</t>
+        </is>
+      </c>
+      <c r="L126" s="13" t="n">
+        <v>4797624.0</v>
+      </c>
+      <c r="M126" s="13" t="n">
+        <v>448689.0</v>
+      </c>
+      <c r="N126" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O126" s="13" t="n">
+        <v>5246313.0</v>
+      </c>
+      <c r="P126" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q126" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="4" t="n">
+        <v>121.0</v>
+      </c>
+      <c r="B127" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C127" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D127" s="7" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="E127" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F127" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H127" s="7"/>
+      <c r="I127" s="6"/>
+      <c r="J127" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K127" s="6"/>
+      <c r="L127" s="13" t="n">
+        <v>1.0657357E7</v>
+      </c>
+      <c r="M127" s="13" t="n">
+        <v>1025737.0</v>
+      </c>
+      <c r="N127" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O127" s="13" t="n">
+        <v>1.1683094E7</v>
+      </c>
+      <c r="P127" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q127" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="4" t="n">
+        <v>122.0</v>
+      </c>
+      <c r="B128" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C128" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D128" s="7" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E128" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F128" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H128" s="7" t="inlineStr">
+        <is>
+          <t>3502556808</t>
+        </is>
+      </c>
+      <c r="I128" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI THỦY HẢI SẢN KIM NGÂN</t>
+        </is>
+      </c>
+      <c r="J128" s="6" t="inlineStr">
+        <is>
+          <t>Số 65A Yên Bái, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K128" s="6"/>
+      <c r="L128" s="13" t="n">
+        <v>8499975.0</v>
+      </c>
+      <c r="M128" s="13" t="n">
+        <v>849998.0</v>
+      </c>
+      <c r="N128" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O128" s="13" t="n">
+        <v>9349973.0</v>
+      </c>
+      <c r="P128" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q128" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="4" t="n">
+        <v>123.0</v>
+      </c>
+      <c r="B129" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C129" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D129" s="7" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E129" s="7" t="inlineStr">
+        <is>
+          <t>10/01/2026</t>
+        </is>
+      </c>
+      <c r="F129" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H129" s="7" t="inlineStr">
+        <is>
+          <t>077088009229</t>
+        </is>
+      </c>
+      <c r="I129" s="6" t="inlineStr">
+        <is>
+          <t>HỘ KINH DOANH TÂM NGUYỄN (DƯƠNG THẾ HUY)</t>
+        </is>
+      </c>
+      <c r="J129" s="6" t="inlineStr">
+        <is>
+          <t>04 đường Lê Lợi, Phường Vũng Tàu, TP Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K129" s="6"/>
+      <c r="L129" s="13" t="n">
         <v>4.2926212E7</v>
       </c>
-      <c r="M101" s="13" t="n">
+      <c r="M129" s="13" t="n">
         <v>4049441.0</v>
       </c>
-      <c r="N101" s="13" t="n">
-        <v>0.0</v>
-      </c>
-      <c r="O101" s="13" t="n">
+      <c r="N129" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O129" s="13" t="n">
         <v>4.6975653E7</v>
       </c>
-      <c r="P101" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="Q101" s="6" t="inlineStr">
+      <c r="P129" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q129" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="4" t="n">
+        <v>124.0</v>
+      </c>
+      <c r="B130" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C130" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D130" s="7" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="E130" s="7" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="F130" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H130" s="7"/>
+      <c r="I130" s="6"/>
+      <c r="J130" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K130" s="6"/>
+      <c r="L130" s="13" t="n">
+        <v>7309280.0</v>
+      </c>
+      <c r="M130" s="13" t="n">
+        <v>692965.0</v>
+      </c>
+      <c r="N130" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O130" s="13" t="n">
+        <v>8002245.0</v>
+      </c>
+      <c r="P130" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q130" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="4" t="n">
+        <v>125.0</v>
+      </c>
+      <c r="B131" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C131" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D131" s="7" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="E131" s="7" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="F131" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H131" s="7"/>
+      <c r="I131" s="6"/>
+      <c r="J131" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K131" s="6"/>
+      <c r="L131" s="13" t="n">
+        <v>7680857.0</v>
+      </c>
+      <c r="M131" s="13" t="n">
+        <v>735123.0</v>
+      </c>
+      <c r="N131" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O131" s="13" t="n">
+        <v>8415980.0</v>
+      </c>
+      <c r="P131" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q131" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="4" t="n">
+        <v>126.0</v>
+      </c>
+      <c r="B132" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C132" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D132" s="7" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="E132" s="7" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="F132" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H132" s="7"/>
+      <c r="I132" s="6"/>
+      <c r="J132" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K132" s="6"/>
+      <c r="L132" s="13" t="n">
+        <v>8683737.0</v>
+      </c>
+      <c r="M132" s="13" t="n">
+        <v>862355.0</v>
+      </c>
+      <c r="N132" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O132" s="13" t="n">
+        <v>9546092.0</v>
+      </c>
+      <c r="P132" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q132" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="4" t="n">
+        <v>127.0</v>
+      </c>
+      <c r="B133" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C133" s="6" t="inlineStr">
+        <is>
+          <t>C26MTD</t>
+        </is>
+      </c>
+      <c r="D133" s="7" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="E133" s="7" t="inlineStr">
+        <is>
+          <t>12/01/2026</t>
+        </is>
+      </c>
+      <c r="F133" s="7" t="inlineStr">
+        <is>
+          <t>3502550210</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THẠNH HƯƠNG BẾN ĐÌNH</t>
+        </is>
+      </c>
+      <c r="H133" s="7"/>
+      <c r="I133" s="6"/>
+      <c r="J133" s="6" t="inlineStr">
+        <is>
+          <t>khách lẻ không lấy hóa đơn</t>
+        </is>
+      </c>
+      <c r="K133" s="6"/>
+      <c r="L133" s="13" t="n">
+        <v>1.2795683E7</v>
+      </c>
+      <c r="M133" s="13" t="n">
+        <v>1223291.0</v>
+      </c>
+      <c r="N133" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O133" s="13" t="n">
+        <v>1.4018974E7</v>
+      </c>
+      <c r="P133" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q133" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
